--- a/Result/profitability/3481.xlsx
+++ b/Result/profitability/3481.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3175</v>
+        <v>0.3825</v>
       </c>
       <c r="N2" t="n">
-        <v>8.891249999999999</v>
+        <v>9.58375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4675</v>
+        <v>0.40625</v>
       </c>
       <c r="N3" t="n">
-        <v>9.325000000000001</v>
+        <v>10.8375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3387499999999999</v>
+        <v>0.395</v>
       </c>
       <c r="N4" t="n">
-        <v>9.552500000000002</v>
+        <v>10.42625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.65</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2425</v>
+        <v>0.32625</v>
       </c>
       <c r="N5" t="n">
-        <v>8.440000000000001</v>
+        <v>9.212500000000002</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.83</v>
       </c>
       <c r="M6" t="n">
-        <v>0.15125</v>
+        <v>0.22125</v>
       </c>
       <c r="N6" t="n">
-        <v>6.900000000000001</v>
+        <v>7.733750000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.45</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09374999999999997</v>
+        <v>0.165</v>
       </c>
       <c r="N7" t="n">
-        <v>6.087500000000001</v>
+        <v>6.772500000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.34</v>
       </c>
       <c r="M8" t="n">
-        <v>0.13625</v>
+        <v>0.1825</v>
       </c>
       <c r="N8" t="n">
-        <v>5.762500000000001</v>
+        <v>5.778750000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.87</v>
       </c>
       <c r="M10" t="n">
-        <v>0.09249999999999997</v>
+        <v>0.0925</v>
       </c>
       <c r="N10" t="n">
         <v>4.190000000000001</v>
@@ -1775,7 +1775,7 @@
         <v>0.14875</v>
       </c>
       <c r="N11" t="n">
-        <v>4.26125</v>
+        <v>4.261250000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>-0.59</v>
       </c>
       <c r="M12" t="n">
-        <v>0.07124999999999997</v>
+        <v>0.07124999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>4.126250000000001</v>
@@ -2026,7 +2026,7 @@
         <v>-3.72</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3125000000000001</v>
+        <v>-0.3125</v>
       </c>
       <c r="N13" t="n">
         <v>3.436250000000001</v>
@@ -9828,6 +9828,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>63700</v>
+      </c>
+      <c r="D75" t="n">
+        <v>54424</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9275</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1633</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>173</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1806</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4532</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.23875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.17375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3699999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.1300000000000008</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.009009009009009139</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6699999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-6.699999999999999</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.737470167064439</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
